--- a/backend/data/Item_Master.xlsx
+++ b/backend/data/Item_Master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,168 +446,723 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Unit of Measure</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Unit Price (USD)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Unit of Measure</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Standard Cost</t>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ITEM001</t>
+          <t>ITM-1001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Laptop Computer</t>
+          <t>Heavy Duty Steel Bolt M12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Fasteners</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>PCE</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>1200</v>
+          <t>Each</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ITEM002</t>
+          <t>ITM-1002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Desktop Monitor</t>
+          <t>Stainless Steel Nut M12</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Fasteners</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>PCE</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>300</v>
+          <t>Each</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ITEM003</t>
+          <t>ITM-1003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Wireless Mouse</t>
+          <t>Industrial Lubricant 5L</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>PCE</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>25</v>
+          <t>Can</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ITEM004</t>
+          <t>ITM-1004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Keyboard</t>
+          <t>Safety Gloves (L)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>PCE</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>75</v>
+          <t>Pair</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ITEM005</t>
+          <t>ITM-1005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>USB Cable</t>
+          <t>PVC Pipe 50mm x 3m</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Plumbing</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>PCE</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
+          <t>Length</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ITM-1006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Electrical Cable 2.5mm 100m</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>95</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ITM-1007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LED Floodlight 50W</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>34</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ITM-1008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Concrete Mix 25kg</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Bag</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ITM-1009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Paint Primer White 10L</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Paint</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Can</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>28</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ITM-1010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Angle Grinder Disc 115mm</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Tools</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Each</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ITM-1011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Fire Extinguisher 2kg</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>42</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ITM-1012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Drill Bit Set HSS 13pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Tools</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ITM-1013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Cable Ties 300mm (100pk)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Pack</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ITM-1014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PPE Hard Hat Yellow</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ITM-1015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Silicone Sealant 300ml</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Tube</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ITM-2001</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Steel Washer M12</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Fasteners</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Each</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2023-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ITM-2002</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Industrial Lubricant 1L (Old)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Can</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
         <v>5</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2022-12-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ITM-2003</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Halogen Floodlight 500W</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>55</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ITM-2004</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PVC Pipe 50mm x 2m (Old Spec)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Plumbing</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Length</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2022-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ITM-2005</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Asbestos Cement Sheet</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Sheet</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2021-01-01</t>
+        </is>
       </c>
     </row>
   </sheetData>
